--- a/data/trans_dic/P56$nadie-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P56$nadie-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,64</t>
+          <t>0,0; 39,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,45</t>
+          <t>0,0; 20,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,31</t>
+          <t>0,0; 43,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,95; 20,02</t>
+          <t>1,81; 16,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,6</t>
+          <t>0,0; 25,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,83; 32,64</t>
+          <t>8,94; 31,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,1; 47,86</t>
+          <t>17,62; 47,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 10,78</t>
+          <t>2,0; 11,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,54; 22,57</t>
+          <t>2,58; 23,73</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,22; 24,08</t>
+          <t>7,11; 23,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,55; 35,6</t>
+          <t>13,99; 36,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,77; 10,56</t>
+          <t>3,36; 11,5</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,56</t>
+          <t>0,0; 15,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,28</t>
+          <t>0,0; 8,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 18,08</t>
+          <t>2,91; 19,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 9,72</t>
+          <t>1,75; 11,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,96; 21,43</t>
+          <t>5,03; 20,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 7,19</t>
+          <t>1,41; 8,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,91; 20,41</t>
+          <t>6,86; 20,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 6,55</t>
+          <t>2,62; 6,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,27; 16,29</t>
+          <t>4,55; 16,72</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 6,35</t>
+          <t>1,46; 6,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,58; 16,75</t>
+          <t>6,78; 17,57</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,01; 6,45</t>
+          <t>2,87; 6,7</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 15,97</t>
+          <t>1,93; 16,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,19</t>
+          <t>0,0; 8,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,62; 17,8</t>
+          <t>3,2; 16,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,72; 9,75</t>
+          <t>2,71; 9,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,12; 19,33</t>
+          <t>4,9; 18,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,65; 10,71</t>
+          <t>3,64; 10,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,85; 24,07</t>
+          <t>11,01; 23,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,03; 6,81</t>
+          <t>3,12; 6,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,49; 14,98</t>
+          <t>5,42; 15,18</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,23; 8,59</t>
+          <t>3,15; 8,49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,75; 19,51</t>
+          <t>9,5; 19,46</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,41; 6,71</t>
+          <t>3,41; 6,72</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2205</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>3377</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4948</t>
+          <t>5622</t>
         </is>
       </c>
     </row>
@@ -1363,62 +1363,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4714</t>
+          <t>0; 5023</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4168</t>
+          <t>0; 4326</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 7028</t>
+          <t>0; 9204</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>579; 5936</t>
+          <t>562; 5234</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5650</t>
+          <t>0; 5614</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3722; 13754</t>
+          <t>3767; 13142</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7456; 19709</t>
+          <t>7256; 19438</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>978; 5712</t>
+          <t>1190; 6687</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>889; 7883</t>
+          <t>900; 8290</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4589; 15304</t>
+          <t>4522; 15043</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8441; 22172</t>
+          <t>8710; 22710</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2285; 8729</t>
+          <t>3036; 10398</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t>3701</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8839</t>
+          <t>9320</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12186</t>
+          <t>13022</t>
         </is>
       </c>
     </row>
@@ -1571,62 +1571,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5512</t>
+          <t>0; 5416</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4724</t>
+          <t>0; 4967</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>895; 9219</t>
+          <t>1487; 9768</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1257; 7039</t>
+          <t>1359; 8598</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3543; 15321</t>
+          <t>3594; 14361</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2223; 11721</t>
+          <t>2298; 13696</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9027; 26658</t>
+          <t>8964; 27069</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5557; 12978</t>
+          <t>5661; 14128</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4569; 17414</t>
+          <t>4859; 17867</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2345; 13985</t>
+          <t>3217; 13756</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11953; 30411</t>
+          <t>12318; 31901</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8154; 17447</t>
+          <t>8422; 19680</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>5947</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11582</t>
+          <t>12697</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17135</t>
+          <t>18644</t>
         </is>
       </c>
     </row>
@@ -1779,62 +1779,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>929; 7709</t>
+          <t>930; 7811</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 7218</t>
+          <t>0; 6366</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1886; 12832</t>
+          <t>2310; 12109</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2775; 9954</t>
+          <t>2947; 10199</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4787; 18084</t>
+          <t>4581; 17262</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7495; 21985</t>
+          <t>7468; 22350</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18642; 41348</t>
+          <t>18906; 41034</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7607; 17087</t>
+          <t>8592; 19055</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7792; 21243</t>
+          <t>7687; 21536</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9166; 24381</t>
+          <t>8925; 24093</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23786; 47572</t>
+          <t>23168; 47464</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12036; 23709</t>
+          <t>13099; 25813</t>
         </is>
       </c>
     </row>
